--- a/memo/資料/レベルデザイン/Book1.xlsx
+++ b/memo/資料/レベルデザイン/Book1.xlsx
@@ -1,33 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0be891feb02739f/エースコンバットもどき/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\はこんばっと\memo\資料\レベルデザイン\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="501" documentId="8_{AE8CC9B5-C362-4432-B53B-768F998D3DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4FEFCB3-7469-4842-A3F8-FD87AB27EAAE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A2C33D-41C9-44D2-A3AB-A3C701808FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{6ED9750B-2395-41CA-B30F-BEAE79245202}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{6ED9750B-2395-41CA-B30F-BEAE79245202}"/>
   </bookViews>
   <sheets>
-    <sheet name="HUD-2" sheetId="1" r:id="rId1"/>
+    <sheet name="HUD画像" sheetId="1" r:id="rId1"/>
     <sheet name="HUD" sheetId="2" r:id="rId2"/>
     <sheet name="MSLUI" sheetId="8" r:id="rId3"/>
     <sheet name="Config" sheetId="4" r:id="rId4"/>
     <sheet name="MSL" sheetId="3" r:id="rId5"/>
     <sheet name="Sheet4" sheetId="15" r:id="rId6"/>
-    <sheet name="SOD" sheetId="5" r:id="rId7"/>
-    <sheet name="CM" sheetId="6" r:id="rId8"/>
-    <sheet name="Sheet8" sheetId="9" r:id="rId9"/>
-    <sheet name="Sheet9" sheetId="10" r:id="rId10"/>
-    <sheet name="Sheet10" sheetId="11" r:id="rId11"/>
-    <sheet name="Sheet1" sheetId="12" r:id="rId12"/>
-    <sheet name="Sheet3" sheetId="14" r:id="rId13"/>
-    <sheet name="Sheet2" sheetId="13" r:id="rId14"/>
-    <sheet name="Sheet5" sheetId="16" r:id="rId15"/>
+    <sheet name="CM" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
   <si>
     <t>計器情報</t>
     <rPh sb="0" eb="4">
@@ -1047,13 +1039,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>手動炸裂</t>
-    <rPh sb="0" eb="4">
-      <t>シュドウサクレツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>〇ボタンで発射する武装を切り替えます</t>
     <rPh sb="5" eb="7">
       <t>ハッシャ</t>
@@ -1070,61 +1055,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>No.2　対空無誘導爆弾　AUGB (anti Air UnGaidance Bomb) (編集済)2025年10月14日 火曜日 16:03</t>
-  </si>
-  <si>
-    <t>No.4 高度依存ミサイル補正システム（Altitude-Adjusted Missile Dynamics）</t>
-  </si>
-  <si>
-    <t>もうちょっとゲーム的に……エースコンバットにおいてSFFSは発射した高度によって加害範囲に補正がかかる感じだったと思うのでそれを対空ミサイルで考えて速度と誘導角速度に補正を加える</t>
-  </si>
-  <si>
-    <t>まさに「SFFSの高度補正を、対空兵装（AAM）に転用」するっていうゲーム的アレンジですね。</t>
-  </si>
-  <si>
-    <t>現実のロフト弾道というより、「発射高度が高いほど弾道性能が向上する」というAce Combat流の“高さボーナス物理”を誘導</t>
-  </si>
-  <si>
-    <t>No.5　弾速を正弦波みたいな感じにする</t>
-  </si>
-  <si>
-    <t>No.6　ウィスキーピーク基準のSACLOS誘導</t>
-  </si>
-  <si>
-    <t>No.7　飛翔中一回だけ誘導角速度リミッターをなくす（高初速・低誘導力でやってみるとたのしそう） (編集済)2025年10月15日 水曜日 9:14</t>
-  </si>
-  <si>
-    <t>No.8　誘導した角速度を累計した値によって威力を減衰させれば偏差射撃の価値が上がるかも</t>
-  </si>
-  <si>
-    <t>No.9　ナパーム爆弾（NPB）のノリ</t>
-  </si>
-  <si>
-    <t>慣性で攻撃判定が前に進む</t>
-  </si>
-  <si>
-    <t>昨日の配信からこれほしいな……とおもったもの</t>
-  </si>
-  <si>
-    <t>・ボスゲージ</t>
-  </si>
-  <si>
-    <t>・爆発</t>
-  </si>
-  <si>
-    <t>・ミス表示</t>
-  </si>
-  <si>
-    <t>・スコア</t>
-  </si>
-  <si>
-    <t>あと現状敵の攻撃が激しいのでスコアを追加するときは被ダメ*時間経過でマイナス補正をかけるかんじがいいかも？</t>
-  </si>
-  <si>
-    <t>特殊兵装のブレーンストーミング！　No.1　空域制圧弾　ASSV(Air Space Suppression Vessel)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>純比例航法について</t>
     <rPh sb="0" eb="5">
       <t>ジュンヒレイコウホウ</t>
@@ -1325,109 +1255,6 @@
     </rPh>
     <rPh sb="4" eb="5">
       <t>ズ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>No.3　対空自己鍛造スタンドオフ投射兵装　ASFS　（anti Air Stand-off Forward Firing Submunition） (編集済)2025年10月14日 火曜日 16:04</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>フレアのシステム刷新</t>
-    <rPh sb="8" eb="10">
-      <t>サッシン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>旧）</t>
-    <rPh sb="0" eb="1">
-      <t>キュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>フレア発射時にミサイルとプレイヤーのロックオン制御スクリプトにアクセス</t>
-    <rPh sb="3" eb="6">
-      <t>ハッシャジ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>セイギョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>それぞれターゲットをフレアに移す抽選を行う</t>
-    <rPh sb="14" eb="15">
-      <t>ウツ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>チュウセン</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>オコナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>新）</t>
-    <rPh sb="0" eb="1">
-      <t>シン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ミサイル制御スクリプトにおいて</t>
-    <rPh sb="4" eb="6">
-      <t>セイギョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>オブジェクトマネージャーからミサイルと敵のオブジェクトを取得</t>
-    <rPh sb="19" eb="20">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>シュトク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>制御スクリプトから熱量、彼我の座標差＝距離を取得</t>
-    <rPh sb="0" eb="2">
-      <t>セイギョ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ネツリョウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ヒガ</t>
-    </rPh>
-    <rPh sb="15" eb="18">
-      <t>ザヒョウサ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>キョリ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>シュトク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>距離減衰を加味して最大熱量のオブジェクトにターゲットを更新</t>
-    <rPh sb="0" eb="4">
-      <t>キョリゲンスイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カミ</t>
-    </rPh>
-    <rPh sb="9" eb="13">
-      <t>サイダイネツリョウ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>コウシン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2920,1352 +2747,6 @@
         </xdr:txBody>
       </xdr:sp>
     </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>221626</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>167046</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>160975</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>31121</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="フリーフォーム: 図形 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B0A9DF6-11E5-4C22-B90D-9609AC7DCCDA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="5925045">
-          <a:off x="6521951" y="334196"/>
-          <a:ext cx="1054700" cy="4054149"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst>
-            <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-            <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-            <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-            <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-            <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-            <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-          </a:gdLst>
-          <a:ahLst/>
-          <a:cxnLst>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX0" y="connsiteY0"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX1" y="connsiteY1"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX2" y="connsiteY2"/>
-            </a:cxn>
-          </a:cxnLst>
-          <a:rect l="l" t="t" r="r" b="b"/>
-          <a:pathLst>
-            <a:path w="1120406" h="6096000">
-              <a:moveTo>
-                <a:pt x="91706" y="6096000"/>
-              </a:moveTo>
-              <a:cubicBezTo>
-                <a:pt x="10743" y="4841875"/>
-                <a:pt x="-70219" y="3587750"/>
-                <a:pt x="101231" y="2571750"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="272681" y="1555750"/>
-                <a:pt x="993406" y="392112"/>
-                <a:pt x="1120406" y="0"/>
-              </a:cubicBezTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>385089</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>184661</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>544291</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>6742</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="二等辺三角形 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F480828A-C04A-4ED7-AD88-880903BE665C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="5242868">
-          <a:off x="9454762" y="3364138"/>
-          <a:ext cx="536456" cy="845002"/>
-        </a:xfrm>
-        <a:prstGeom prst="triangle">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FF0000"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>496201</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>4501</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>255722</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>48764</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="楕円 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38E24A82-51FC-4B8A-9CAC-7B0835CA2763}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8040001" y="2385751"/>
-          <a:ext cx="1816921" cy="1711138"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="4472C4">
-            <a:alpha val="27843"/>
-          </a:srgbClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>122242</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>263689</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>180717</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="二等辺三角形 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F34FA6E-718C-43D7-A8A7-7A345F05E71F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="5400000">
-          <a:off x="5055607" y="1153110"/>
-          <a:ext cx="534725" cy="854239"/>
-        </a:xfrm>
-        <a:prstGeom prst="triangle">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="4472C4"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>621676</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>225779</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>561025</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>89854</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="フリーフォーム: 図形 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C14A99AB-607D-4BD5-9BC1-BB2E5DAC232A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="5925045">
-          <a:off x="5550401" y="392929"/>
-          <a:ext cx="1054700" cy="4054149"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst>
-            <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-            <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-            <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-            <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-            <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-            <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-          </a:gdLst>
-          <a:ahLst/>
-          <a:cxnLst>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX0" y="connsiteY0"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX1" y="connsiteY1"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX2" y="connsiteY2"/>
-            </a:cxn>
-          </a:cxnLst>
-          <a:rect l="l" t="t" r="r" b="b"/>
-          <a:pathLst>
-            <a:path w="1120406" h="6096000">
-              <a:moveTo>
-                <a:pt x="91706" y="6096000"/>
-              </a:moveTo>
-              <a:cubicBezTo>
-                <a:pt x="10743" y="4841875"/>
-                <a:pt x="-70219" y="3587750"/>
-                <a:pt x="101231" y="2571750"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="272681" y="1555750"/>
-                <a:pt x="993406" y="392112"/>
-                <a:pt x="1120406" y="0"/>
-              </a:cubicBezTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>99339</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>5269</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>258541</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>65475</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="二等辺三角形 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07804AF2-0AC5-482E-A51A-E7F6BD429BC3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="5242868">
-          <a:off x="8483212" y="3422871"/>
-          <a:ext cx="536456" cy="845002"/>
-        </a:xfrm>
-        <a:prstGeom prst="triangle">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FF0000"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>210451</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>63234</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>655772</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>107497</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="楕円 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB234930-BECE-4D67-9E8D-B1CDA03AD711}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7068451" y="2444484"/>
-          <a:ext cx="1816921" cy="1711138"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="4472C4">
-            <a:alpha val="27843"/>
-          </a:srgbClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>663739</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>1325</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="二等辺三角形 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E1C5AC4-D070-4AAA-9B9A-B0995736487B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="5400000">
-          <a:off x="4084057" y="1211843"/>
-          <a:ext cx="534725" cy="854239"/>
-        </a:xfrm>
-        <a:prstGeom prst="triangle">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="4472C4"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>680364</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>100519</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>153766</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>160725</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="二等辺三角形 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E342F57F-7530-E28D-65EB-07794DB71B83}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="5242868">
-          <a:off x="10435837" y="2565621"/>
-          <a:ext cx="536456" cy="845002"/>
-        </a:xfrm>
-        <a:prstGeom prst="triangle">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FF0000"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>391426</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>129909</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>150947</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>174172</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="楕円 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2377CF4-A1E5-61AB-F346-3C1FEE9E8845}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8621026" y="2511159"/>
-          <a:ext cx="1816921" cy="1711138"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="4472C4">
-            <a:alpha val="27843"/>
-          </a:srgbClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>99340</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>52893</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>258542</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>113099</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="二等辺三角形 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D160AC4-F96B-C077-9CDC-4E24840D22F9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="5242868">
-          <a:off x="13283813" y="3470495"/>
-          <a:ext cx="536456" cy="845002"/>
-        </a:xfrm>
-        <a:prstGeom prst="triangle">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FF0000"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>524776</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>53709</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>284297</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>97972</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="楕円 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD2B89DB-35C7-BFA9-7B2E-CC90DEBB4818}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10125976" y="2673084"/>
-          <a:ext cx="1816921" cy="1711138"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="4472C4">
-            <a:alpha val="27843"/>
-          </a:srgbClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>39001</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>101334</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>484322</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>145597</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="楕円 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D89E0687-4E9E-AE3D-BF75-DDCB2EC0C6D5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11697601" y="2720709"/>
-          <a:ext cx="1816921" cy="1711138"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="4472C4">
-            <a:alpha val="27843"/>
-          </a:srgbClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>523875</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="5" name="グループ化 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3AA34AF-23F3-086A-ED62-3568AD16386F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="3600450" y="942975"/>
-          <a:ext cx="6524625" cy="1266825"/>
-          <a:chOff x="2266950" y="1552575"/>
-          <a:chExt cx="6524625" cy="1266825"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="3" name="直線コネクタ 2">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE0984A6-9215-A18E-0FD1-286DC5E3DDDC}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr/>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm flipV="1">
-            <a:off x="2266950" y="1562100"/>
-            <a:ext cx="6515100" cy="1257300"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln w="228600">
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:alpha val="42000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="4" name="直線コネクタ 3">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D53B5D3-4CA4-B2C4-FF95-12E11B3F908F}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr/>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm flipV="1">
-            <a:off x="2276475" y="1552575"/>
-            <a:ext cx="6515100" cy="1257300"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln w="88900"/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>638088</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="フリーフォーム: 図形 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B42B9C5-C3B4-EC5E-6F90-CA251DEB7B26}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9648825" y="942975"/>
-          <a:ext cx="1276263" cy="5638800"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst>
-            <a:gd name="connsiteX0" fmla="*/ 476250 w 1276263"/>
-            <a:gd name="connsiteY0" fmla="*/ 0 h 5638800"/>
-            <a:gd name="connsiteX1" fmla="*/ 1266825 w 1276263"/>
-            <a:gd name="connsiteY1" fmla="*/ 2781300 h 5638800"/>
-            <a:gd name="connsiteX2" fmla="*/ 0 w 1276263"/>
-            <a:gd name="connsiteY2" fmla="*/ 5638800 h 5638800"/>
-          </a:gdLst>
-          <a:ahLst/>
-          <a:cxnLst>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX0" y="connsiteY0"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX1" y="connsiteY1"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX2" y="connsiteY2"/>
-            </a:cxn>
-          </a:cxnLst>
-          <a:rect l="l" t="t" r="r" b="b"/>
-          <a:pathLst>
-            <a:path w="1276263" h="5638800">
-              <a:moveTo>
-                <a:pt x="476250" y="0"/>
-              </a:moveTo>
-              <a:cubicBezTo>
-                <a:pt x="911225" y="920750"/>
-                <a:pt x="1346200" y="1841500"/>
-                <a:pt x="1266825" y="2781300"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="1187450" y="3721100"/>
-                <a:pt x="239712" y="5184775"/>
-                <a:pt x="0" y="5638800"/>
-              </a:cubicBezTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:noFill/>
-        <a:ln w="76200">
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="58000"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>638175</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="20483" name="AutoShape 3" descr="画像を出力する">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44C535F4-1672-CF00-B763-BD0D0209AC07}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6858000" y="2143125"/>
-          <a:ext cx="15039975" cy="7553325"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="20485" name="AutoShape 5" descr="画像を出力する">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCD9617A-2869-E163-F25C-C403FAACB24E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2057400" y="952500"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="20486" name="AutoShape 6" descr="画像を出力する">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61812A03-E9D5-5380-1C4D-73B91CEDCDF6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2057400" y="952500"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>375003</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>555815</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>176142</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B2EBDE0-6124-591D-539F-98AAE1134FDF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1062460" y="0"/>
-          <a:ext cx="4993007" cy="2578099"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -6564,7 +5045,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Config!$F$6:$F$15" spid="_x0000_s8306"/>
+                  <a14:cameraTool cellRange="Config!$F$6:$F$15" spid="_x0000_s8308"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -8870,5014 +7351,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>365494</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="フリーフォーム: 図形 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BA7187C-7A8E-0600-CC61-1980BC6FD72D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6537694" y="923925"/>
-          <a:ext cx="1120406" cy="6096000"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst>
-            <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-            <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-            <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-            <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-            <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-            <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-          </a:gdLst>
-          <a:ahLst/>
-          <a:cxnLst>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX0" y="connsiteY0"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX1" y="connsiteY1"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX2" y="connsiteY2"/>
-            </a:cxn>
-          </a:cxnLst>
-          <a:rect l="l" t="t" r="r" b="b"/>
-          <a:pathLst>
-            <a:path w="1120406" h="6096000">
-              <a:moveTo>
-                <a:pt x="91706" y="6096000"/>
-              </a:moveTo>
-              <a:cubicBezTo>
-                <a:pt x="10743" y="4841875"/>
-                <a:pt x="-70219" y="3587750"/>
-                <a:pt x="101231" y="2571750"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="272681" y="1555750"/>
-                <a:pt x="993406" y="392112"/>
-                <a:pt x="1120406" y="0"/>
-              </a:cubicBezTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>97023</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>173222</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>20823</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>103003</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="フリーフォーム: 図形 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5A51080-09B3-B8C1-F99F-6264F5231B3B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="3229062">
-          <a:off x="8757020" y="1257300"/>
-          <a:ext cx="1120406" cy="6096000"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst>
-            <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-            <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-            <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-            <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-            <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-            <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-          </a:gdLst>
-          <a:ahLst/>
-          <a:cxnLst>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX0" y="connsiteY0"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX1" y="connsiteY1"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX2" y="connsiteY2"/>
-            </a:cxn>
-          </a:cxnLst>
-          <a:rect l="l" t="t" r="r" b="b"/>
-          <a:pathLst>
-            <a:path w="1120406" h="6096000">
-              <a:moveTo>
-                <a:pt x="91706" y="6096000"/>
-              </a:moveTo>
-              <a:cubicBezTo>
-                <a:pt x="10743" y="4841875"/>
-                <a:pt x="-70219" y="3587750"/>
-                <a:pt x="101231" y="2571750"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="272681" y="1555750"/>
-                <a:pt x="993406" y="392112"/>
-                <a:pt x="1120406" y="0"/>
-              </a:cubicBezTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>292072</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>1594</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>490688</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>78821</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="フリーフォーム: 図形 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{536B3946-9302-3E51-CAD3-40F6D50E4989}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="3897579">
-          <a:off x="8344241" y="1455375"/>
-          <a:ext cx="553477" cy="4313416"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst>
-            <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-            <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-            <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-            <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-            <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-            <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-          </a:gdLst>
-          <a:ahLst/>
-          <a:cxnLst>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX0" y="connsiteY0"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX1" y="connsiteY1"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX2" y="connsiteY2"/>
-            </a:cxn>
-          </a:cxnLst>
-          <a:rect l="l" t="t" r="r" b="b"/>
-          <a:pathLst>
-            <a:path w="1120406" h="6096000">
-              <a:moveTo>
-                <a:pt x="91706" y="6096000"/>
-              </a:moveTo>
-              <a:cubicBezTo>
-                <a:pt x="10743" y="4841875"/>
-                <a:pt x="-70219" y="3587750"/>
-                <a:pt x="101231" y="2571750"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="272681" y="1555750"/>
-                <a:pt x="993406" y="392112"/>
-                <a:pt x="1120406" y="0"/>
-              </a:cubicBezTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>573888</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>107453</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>613389</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>128142</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="フリーフォーム: 図形 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46B67321-39EA-654E-5FBB-407DC0AAAAC8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="3897579">
-          <a:off x="7769907" y="1464884"/>
-          <a:ext cx="735064" cy="2782701"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst>
-            <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-            <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-            <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-            <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-            <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-            <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-          </a:gdLst>
-          <a:ahLst/>
-          <a:cxnLst>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX0" y="connsiteY0"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX1" y="connsiteY1"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX2" y="connsiteY2"/>
-            </a:cxn>
-          </a:cxnLst>
-          <a:rect l="l" t="t" r="r" b="b"/>
-          <a:pathLst>
-            <a:path w="1120406" h="6096000">
-              <a:moveTo>
-                <a:pt x="91706" y="6096000"/>
-              </a:moveTo>
-              <a:cubicBezTo>
-                <a:pt x="10743" y="4841875"/>
-                <a:pt x="-70219" y="3587750"/>
-                <a:pt x="101231" y="2571750"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="272681" y="1555750"/>
-                <a:pt x="993406" y="392112"/>
-                <a:pt x="1120406" y="0"/>
-              </a:cubicBezTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>261473</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>103457</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>440026</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>84513</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="フリーフォーム: 図形 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08C9C737-8567-8FEC-4668-5A0078A6BF4B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="3897579">
-          <a:off x="7546834" y="1342971"/>
-          <a:ext cx="695431" cy="1550153"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst>
-            <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-            <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-            <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-            <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-            <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-            <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-          </a:gdLst>
-          <a:ahLst/>
-          <a:cxnLst>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX0" y="connsiteY0"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX1" y="connsiteY1"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX2" y="connsiteY2"/>
-            </a:cxn>
-          </a:cxnLst>
-          <a:rect l="l" t="t" r="r" b="b"/>
-          <a:pathLst>
-            <a:path w="1120406" h="6096000">
-              <a:moveTo>
-                <a:pt x="91706" y="6096000"/>
-              </a:moveTo>
-              <a:cubicBezTo>
-                <a:pt x="10743" y="4841875"/>
-                <a:pt x="-70219" y="3587750"/>
-                <a:pt x="101231" y="2571750"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="272681" y="1555750"/>
-                <a:pt x="993406" y="392112"/>
-                <a:pt x="1120406" y="0"/>
-              </a:cubicBezTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>478367</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>632883</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="二等辺三角形 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FFEF9B0-2FF9-B151-7271-1F3721AF4347}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="5242868">
-          <a:off x="13010092" y="2614083"/>
-          <a:ext cx="543984" cy="842433"/>
-        </a:xfrm>
-        <a:prstGeom prst="triangle">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FF0000"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>161926</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>619125</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>57151</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="楕円 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD4D08AF-73A2-B790-09BE-A41D326B6F5E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8705850" y="2066926"/>
-          <a:ext cx="142875" cy="133350"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="楕円 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C92B41FE-022D-AC5E-7A33-D01B790915F0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7534275" y="704850"/>
-          <a:ext cx="323850" cy="333375"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>152401</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>47626</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="楕円 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B3D5515-9562-B249-78EF-D4C0E921D8FE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9505950" y="2533651"/>
-          <a:ext cx="142875" cy="133350"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>19051</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>152401</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="楕円 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CE5A43D-A0B2-0936-5C69-949C0F855B15}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10629900" y="2876551"/>
-          <a:ext cx="142875" cy="133350"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>9526</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>142876</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="楕円 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{568BE892-C3D1-0A09-8897-44FBE51F8CAB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12058650" y="2867026"/>
-          <a:ext cx="142875" cy="133350"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>162983</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>70909</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>10583</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="二等辺三角形 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F382869-5BA7-1218-0E90-1A5692BF791A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6354233" y="6399742"/>
-          <a:ext cx="535517" cy="859366"/>
-        </a:xfrm>
-        <a:prstGeom prst="triangle">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="4472C4"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>25</xdr:col>
-          <xdr:colOff>280939</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>195311</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>39</xdr:col>
-          <xdr:colOff>290464</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>204835</xdr:rowOff>
-        </xdr:to>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="19" name="図 18">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B1439C6-396B-7CB7-76D4-CE058E297192}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-              <a:extLst>
-                <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$G$2:$T$32" spid="_x0000_s5271"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-            <a:srcRect/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="17599121" y="680220"/>
-              <a:ext cx="9707707" cy="7525615"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>1507</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>214271</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>360001</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>174834</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="フリーフォーム: 図形 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C80C966B-7640-4FD9-A8AC-36231C091305}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="4111505">
-          <a:off x="8625335" y="-599057"/>
-          <a:ext cx="1627438" cy="5159094"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst>
-            <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-            <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-            <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-            <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-            <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-            <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-          </a:gdLst>
-          <a:ahLst/>
-          <a:cxnLst>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX0" y="connsiteY0"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX1" y="connsiteY1"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX2" y="connsiteY2"/>
-            </a:cxn>
-          </a:cxnLst>
-          <a:rect l="l" t="t" r="r" b="b"/>
-          <a:pathLst>
-            <a:path w="1120406" h="6096000">
-              <a:moveTo>
-                <a:pt x="91706" y="6096000"/>
-              </a:moveTo>
-              <a:cubicBezTo>
-                <a:pt x="10743" y="4841875"/>
-                <a:pt x="-70219" y="3587750"/>
-                <a:pt x="101231" y="2571750"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="272681" y="1555750"/>
-                <a:pt x="993406" y="392112"/>
-                <a:pt x="1120406" y="0"/>
-              </a:cubicBezTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>78669</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>40323</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>245181</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>102552</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="フリーフォーム: 図形 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0340141A-55DC-414B-BBE1-7BE83ECF9918}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="3897579">
-          <a:off x="7631748" y="297744"/>
-          <a:ext cx="2205354" cy="3595512"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst>
-            <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-            <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-            <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-            <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-            <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-            <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-          </a:gdLst>
-          <a:ahLst/>
-          <a:cxnLst>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX0" y="connsiteY0"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX1" y="connsiteY1"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX2" y="connsiteY2"/>
-            </a:cxn>
-          </a:cxnLst>
-          <a:rect l="l" t="t" r="r" b="b"/>
-          <a:pathLst>
-            <a:path w="1120406" h="6096000">
-              <a:moveTo>
-                <a:pt x="91706" y="6096000"/>
-              </a:moveTo>
-              <a:cubicBezTo>
-                <a:pt x="10743" y="4841875"/>
-                <a:pt x="-70219" y="3587750"/>
-                <a:pt x="101231" y="2571750"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="272681" y="1555750"/>
-                <a:pt x="993406" y="392112"/>
-                <a:pt x="1120406" y="0"/>
-              </a:cubicBezTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>608681</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>1294</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>289622</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>218262</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="フリーフォーム: 図形 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE94AE4B-18DD-4DC0-8D20-F30F3B302765}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="3897579">
-          <a:off x="8379768" y="-435543"/>
-          <a:ext cx="4026968" cy="5853141"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst>
-            <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-            <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-            <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-            <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-            <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-            <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-          </a:gdLst>
-          <a:ahLst/>
-          <a:cxnLst>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX0" y="connsiteY0"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX1" y="connsiteY1"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX2" y="connsiteY2"/>
-            </a:cxn>
-          </a:cxnLst>
-          <a:rect l="l" t="t" r="r" b="b"/>
-          <a:pathLst>
-            <a:path w="1120406" h="6096000">
-              <a:moveTo>
-                <a:pt x="91706" y="6096000"/>
-              </a:moveTo>
-              <a:cubicBezTo>
-                <a:pt x="10743" y="4841875"/>
-                <a:pt x="-70219" y="3587750"/>
-                <a:pt x="101231" y="2571750"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="272681" y="1555750"/>
-                <a:pt x="993406" y="392112"/>
-                <a:pt x="1120406" y="0"/>
-              </a:cubicBezTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>194888</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>97523</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>14368</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>68013</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="フリーフォーム: 図形 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D9199A7-33FA-4F3C-92DF-1C2A093D4846}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="3897579">
-          <a:off x="8768083" y="-1141422"/>
-          <a:ext cx="1875490" cy="5305880"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst>
-            <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-            <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-            <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-            <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-            <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-            <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-          </a:gdLst>
-          <a:ahLst/>
-          <a:cxnLst>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX0" y="connsiteY0"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX1" y="connsiteY1"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="connsiteX2" y="connsiteY2"/>
-            </a:cxn>
-          </a:cxnLst>
-          <a:rect l="l" t="t" r="r" b="b"/>
-          <a:pathLst>
-            <a:path w="1120406" h="6096000">
-              <a:moveTo>
-                <a:pt x="91706" y="6096000"/>
-              </a:moveTo>
-              <a:cubicBezTo>
-                <a:pt x="10743" y="4841875"/>
-                <a:pt x="-70219" y="3587750"/>
-                <a:pt x="101231" y="2571750"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="272681" y="1555750"/>
-                <a:pt x="993406" y="392112"/>
-                <a:pt x="1120406" y="0"/>
-              </a:cubicBezTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>405591</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>10391</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>567034</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="二等辺三角形 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACF58CBD-3499-4341-BD49-F6EB8357A863}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="5242868">
-          <a:off x="12216783" y="2000924"/>
-          <a:ext cx="542059" cy="847243"/>
-        </a:xfrm>
-        <a:prstGeom prst="triangle">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FF0000"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>161884</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>130753</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>304759</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>30308</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="楕円 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05DE765D-28DF-4C1C-99AE-55B69231410F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="161884" y="2988253"/>
-          <a:ext cx="142875" cy="137680"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>119455</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>450232</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>218209</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="楕円 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2617E00E-B20C-42FE-97B8-DCBA30C67BB6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="119455" y="1781175"/>
-          <a:ext cx="330777" cy="342034"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="15" name="直線コネクタ 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70D14D27-59FE-F199-2202-C23D58B83C59}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4229100" y="2066925"/>
-          <a:ext cx="2771775" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="19050"/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>14680</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>466725</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="楕円 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6161F1A8-DD29-0B92-EE8E-E3BCF10C9D1A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11673280" y="342900"/>
-          <a:ext cx="1823645" cy="1733550"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="4472C4">
-            <a:alpha val="27843"/>
-          </a:srgbClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>224230</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="楕円 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B50D9027-81D5-0CD1-1042-BB3140489FEA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11197030" y="923925"/>
-          <a:ext cx="1823645" cy="1733550"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="4472C4">
-            <a:alpha val="27843"/>
-          </a:srgbClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>671905</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="19" name="楕円 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4C99841-534E-A742-4285-C60D639FD093}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13016305" y="2200275"/>
-          <a:ext cx="1823645" cy="1733550"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="4472C4">
-            <a:alpha val="27843"/>
-          </a:srgbClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>281380</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="楕円 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB798B3F-3363-6EDD-C7F2-568E6699A0EC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9882580" y="1400175"/>
-          <a:ext cx="1823645" cy="1733550"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="4472C4">
-            <a:alpha val="27843"/>
-          </a:srgbClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>469859</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>113819</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>640539</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>177897</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="二等辺三角形 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C405095-C4C4-4EF0-B375-F663FC6F39B2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="5400000">
-          <a:off x="4056935" y="1622618"/>
-          <a:ext cx="540328" cy="856480"/>
-        </a:xfrm>
-        <a:prstGeom prst="triangle">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="4472C4"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>613689</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>16554</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>87091</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>76760</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="二等辺三角形 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91F49B7E-0A01-4413-92AF-C3A5C86D5FB5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="5242868">
-          <a:off x="10369162" y="5339156"/>
-          <a:ext cx="536456" cy="845002"/>
-        </a:xfrm>
-        <a:prstGeom prst="triangle">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FF0000"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>308950</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>18489</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="5" name="直線コネクタ 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2717A19-E4F6-46F9-9B49-CF00CC2B213E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3043185" y="1430430"/>
-          <a:ext cx="6659989" cy="19611"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="19050"/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>230360</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>16039</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>50710</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="二等辺三角形 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{828E97BB-9D7E-4B96-AF35-62F98322D036}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="5400000">
-          <a:off x="2750557" y="1023103"/>
-          <a:ext cx="534725" cy="854239"/>
-        </a:xfrm>
-        <a:prstGeom prst="triangle">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="4472C4"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>167868</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>47877</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>437257</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>4482</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="14" name="グループ化 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C78EC14B-DD81-5675-6911-7CF2E1DFA7D1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="5636339" y="1459818"/>
-          <a:ext cx="7104977" cy="3486458"/>
-          <a:chOff x="5636339" y="1459818"/>
-          <a:chExt cx="7104977" cy="3486458"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="2" name="フリーフォーム: 図形 1">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3F2BF56-7748-45F3-A021-9EADA59B86FE}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="2833576">
-            <a:off x="7648320" y="836209"/>
-            <a:ext cx="536972" cy="3303762"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-              <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-              <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-              <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-              <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-              <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX0" y="connsiteY0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX1" y="connsiteY1"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX2" y="connsiteY2"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="l" t="t" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="1120406" h="6096000">
-                <a:moveTo>
-                  <a:pt x="91706" y="6096000"/>
-                </a:moveTo>
-                <a:cubicBezTo>
-                  <a:pt x="10743" y="4841875"/>
-                  <a:pt x="-70219" y="3587750"/>
-                  <a:pt x="101231" y="2571750"/>
-                </a:cubicBezTo>
-                <a:cubicBezTo>
-                  <a:pt x="272681" y="1555750"/>
-                  <a:pt x="993406" y="392112"/>
-                  <a:pt x="1120406" y="0"/>
-                </a:cubicBezTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="3" name="フリーフォーム: 図形 2">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D03E5F9-BFEC-4933-85E8-71484A4289D5}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="7202030">
-            <a:off x="10284991" y="1165680"/>
-            <a:ext cx="1306134" cy="3029338"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-              <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-              <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-              <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-              <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-              <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX0" y="connsiteY0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX1" y="connsiteY1"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX2" y="connsiteY2"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="l" t="t" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="1120406" h="6096000">
-                <a:moveTo>
-                  <a:pt x="91706" y="6096000"/>
-                </a:moveTo>
-                <a:cubicBezTo>
-                  <a:pt x="10743" y="4841875"/>
-                  <a:pt x="-70219" y="3587750"/>
-                  <a:pt x="101231" y="2571750"/>
-                </a:cubicBezTo>
-                <a:cubicBezTo>
-                  <a:pt x="272681" y="1555750"/>
-                  <a:pt x="993406" y="392112"/>
-                  <a:pt x="1120406" y="0"/>
-                </a:cubicBezTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="6" name="楕円 5">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3EF83E9-E4F7-4ACF-B812-09DD56772150}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="10068826" y="2308412"/>
-            <a:ext cx="1812439" cy="1694328"/>
-          </a:xfrm>
-          <a:prstGeom prst="ellipse">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="27843"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="7" name="楕円 6">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54FE2D74-66A4-4374-AD76-263ACDDEDD43}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5636339" y="2630581"/>
-            <a:ext cx="1814680" cy="1691528"/>
-          </a:xfrm>
-          <a:prstGeom prst="ellipse">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="27843"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="8" name="楕円 7">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE04614D-7027-4D80-BE65-DE1EA7C663AF}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="10931118" y="3141569"/>
-            <a:ext cx="1810198" cy="1694329"/>
-          </a:xfrm>
-          <a:prstGeom prst="ellipse">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="27843"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="9" name="楕円 8">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA12703A-DE09-4FFE-85C6-1FED9AC6220E}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="6893639" y="3257550"/>
-            <a:ext cx="1812439" cy="1688726"/>
-          </a:xfrm>
-          <a:prstGeom prst="ellipse">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="27843"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="12" name="フリーフォーム: 図形 11">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4AC5CC83-B1D7-824F-4A4C-1A40B5A4DB76}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="20023133" flipH="1">
-            <a:off x="10218076" y="1461394"/>
-            <a:ext cx="489665" cy="1863170"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-              <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-              <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-              <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-              <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-              <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX0" y="connsiteY0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX1" y="connsiteY1"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX2" y="connsiteY2"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="l" t="t" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="1120406" h="6096000">
-                <a:moveTo>
-                  <a:pt x="91706" y="6096000"/>
-                </a:moveTo>
-                <a:cubicBezTo>
-                  <a:pt x="10743" y="4841875"/>
-                  <a:pt x="-70219" y="3587750"/>
-                  <a:pt x="101231" y="2571750"/>
-                </a:cubicBezTo>
-                <a:cubicBezTo>
-                  <a:pt x="272681" y="1555750"/>
-                  <a:pt x="993406" y="392112"/>
-                  <a:pt x="1120406" y="0"/>
-                </a:cubicBezTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="13" name="フリーフォーム: 図形 12">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE061CA4-6269-63F0-B6AB-D82413A7E40A}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="1226854">
-            <a:off x="8231636" y="1459818"/>
-            <a:ext cx="902441" cy="2815356"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-              <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-              <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-              <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-              <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-              <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX0" y="connsiteY0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX1" y="connsiteY1"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX2" y="connsiteY2"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="l" t="t" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="1120406" h="6096000">
-                <a:moveTo>
-                  <a:pt x="91706" y="6096000"/>
-                </a:moveTo>
-                <a:cubicBezTo>
-                  <a:pt x="10743" y="4841875"/>
-                  <a:pt x="-70219" y="3587750"/>
-                  <a:pt x="101231" y="2571750"/>
-                </a:cubicBezTo>
-                <a:cubicBezTo>
-                  <a:pt x="272681" y="1555750"/>
-                  <a:pt x="993406" y="392112"/>
-                  <a:pt x="1120406" y="0"/>
-                </a:cubicBezTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>212691</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>78441</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>22412</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>228599</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="15" name="グループ化 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{900F3A74-1EE1-E5F5-214F-491CF4D8C5BA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="9782515" y="3843617"/>
-          <a:ext cx="3911073" cy="2268070"/>
-          <a:chOff x="5636339" y="1459818"/>
-          <a:chExt cx="7104977" cy="3486458"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="16" name="フリーフォーム: 図形 15">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08CACCCA-8EDB-9FD4-1658-89F2A1FB1D76}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="2833576">
-            <a:off x="7648320" y="836209"/>
-            <a:ext cx="536972" cy="3303762"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-              <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-              <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-              <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-              <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-              <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX0" y="connsiteY0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX1" y="connsiteY1"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX2" y="connsiteY2"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="l" t="t" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="1120406" h="6096000">
-                <a:moveTo>
-                  <a:pt x="91706" y="6096000"/>
-                </a:moveTo>
-                <a:cubicBezTo>
-                  <a:pt x="10743" y="4841875"/>
-                  <a:pt x="-70219" y="3587750"/>
-                  <a:pt x="101231" y="2571750"/>
-                </a:cubicBezTo>
-                <a:cubicBezTo>
-                  <a:pt x="272681" y="1555750"/>
-                  <a:pt x="993406" y="392112"/>
-                  <a:pt x="1120406" y="0"/>
-                </a:cubicBezTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="17" name="フリーフォーム: 図形 16">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2761A348-DED3-5AC0-EC09-D194416DB624}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="7202030">
-            <a:off x="10284991" y="1165680"/>
-            <a:ext cx="1306134" cy="3029338"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-              <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-              <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-              <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-              <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-              <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX0" y="connsiteY0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX1" y="connsiteY1"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX2" y="connsiteY2"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="l" t="t" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="1120406" h="6096000">
-                <a:moveTo>
-                  <a:pt x="91706" y="6096000"/>
-                </a:moveTo>
-                <a:cubicBezTo>
-                  <a:pt x="10743" y="4841875"/>
-                  <a:pt x="-70219" y="3587750"/>
-                  <a:pt x="101231" y="2571750"/>
-                </a:cubicBezTo>
-                <a:cubicBezTo>
-                  <a:pt x="272681" y="1555750"/>
-                  <a:pt x="993406" y="392112"/>
-                  <a:pt x="1120406" y="0"/>
-                </a:cubicBezTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="18" name="楕円 17">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E41939CA-D0DE-20C9-8EFB-5634883D0840}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="10068826" y="2308412"/>
-            <a:ext cx="1812439" cy="1694328"/>
-          </a:xfrm>
-          <a:prstGeom prst="ellipse">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="27843"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="19" name="楕円 18">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A57564C-456F-22FA-2606-B613901876CE}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5636339" y="2630581"/>
-            <a:ext cx="1814680" cy="1691528"/>
-          </a:xfrm>
-          <a:prstGeom prst="ellipse">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="27843"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="20" name="楕円 19">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8294346D-8EE3-FA03-7341-61039509B1C9}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="10931118" y="3141569"/>
-            <a:ext cx="1810198" cy="1694329"/>
-          </a:xfrm>
-          <a:prstGeom prst="ellipse">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="27843"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="21" name="楕円 20">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D14CB45-21EC-8BDF-7721-F7D0B60BF1EA}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="6893639" y="3257550"/>
-            <a:ext cx="1812439" cy="1688726"/>
-          </a:xfrm>
-          <a:prstGeom prst="ellipse">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="27843"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="22" name="フリーフォーム: 図形 21">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EBA296B-554F-025E-9AA9-92D1C90AC3C6}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="20023133" flipH="1">
-            <a:off x="10218076" y="1461394"/>
-            <a:ext cx="489665" cy="1863170"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-              <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-              <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-              <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-              <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-              <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX0" y="connsiteY0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX1" y="connsiteY1"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX2" y="connsiteY2"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="l" t="t" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="1120406" h="6096000">
-                <a:moveTo>
-                  <a:pt x="91706" y="6096000"/>
-                </a:moveTo>
-                <a:cubicBezTo>
-                  <a:pt x="10743" y="4841875"/>
-                  <a:pt x="-70219" y="3587750"/>
-                  <a:pt x="101231" y="2571750"/>
-                </a:cubicBezTo>
-                <a:cubicBezTo>
-                  <a:pt x="272681" y="1555750"/>
-                  <a:pt x="993406" y="392112"/>
-                  <a:pt x="1120406" y="0"/>
-                </a:cubicBezTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="23" name="フリーフォーム: 図形 22">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90682431-6BB4-4454-9825-962E1B3EC2AA}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="1226854">
-            <a:off x="8231636" y="1459818"/>
-            <a:ext cx="902441" cy="2815356"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-              <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-              <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-              <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-              <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-              <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX0" y="connsiteY0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX1" y="connsiteY1"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX2" y="connsiteY2"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="l" t="t" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="1120406" h="6096000">
-                <a:moveTo>
-                  <a:pt x="91706" y="6096000"/>
-                </a:moveTo>
-                <a:cubicBezTo>
-                  <a:pt x="10743" y="4841875"/>
-                  <a:pt x="-70219" y="3587750"/>
-                  <a:pt x="101231" y="2571750"/>
-                </a:cubicBezTo>
-                <a:cubicBezTo>
-                  <a:pt x="272681" y="1555750"/>
-                  <a:pt x="993406" y="392112"/>
-                  <a:pt x="1120406" y="0"/>
-                </a:cubicBezTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>10986</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>67235</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>504265</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>217393</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="24" name="グループ化 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76F83EE5-2D2F-D6E8-0368-D7B912C35E4A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="8897251" y="3126441"/>
-          <a:ext cx="3911073" cy="2268070"/>
-          <a:chOff x="5636339" y="1459818"/>
-          <a:chExt cx="7104977" cy="3486458"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="25" name="フリーフォーム: 図形 24">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{108E9216-909E-7C93-54EE-7DD8C7F6F40A}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="2833576">
-            <a:off x="7648320" y="836209"/>
-            <a:ext cx="536972" cy="3303762"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-              <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-              <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-              <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-              <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-              <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX0" y="connsiteY0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX1" y="connsiteY1"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX2" y="connsiteY2"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="l" t="t" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="1120406" h="6096000">
-                <a:moveTo>
-                  <a:pt x="91706" y="6096000"/>
-                </a:moveTo>
-                <a:cubicBezTo>
-                  <a:pt x="10743" y="4841875"/>
-                  <a:pt x="-70219" y="3587750"/>
-                  <a:pt x="101231" y="2571750"/>
-                </a:cubicBezTo>
-                <a:cubicBezTo>
-                  <a:pt x="272681" y="1555750"/>
-                  <a:pt x="993406" y="392112"/>
-                  <a:pt x="1120406" y="0"/>
-                </a:cubicBezTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="26" name="フリーフォーム: 図形 25">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BCEBF76-E67A-1CB9-3B8B-C545315CC85C}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="7202030">
-            <a:off x="10284991" y="1165680"/>
-            <a:ext cx="1306134" cy="3029338"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-              <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-              <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-              <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-              <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-              <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX0" y="connsiteY0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX1" y="connsiteY1"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX2" y="connsiteY2"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="l" t="t" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="1120406" h="6096000">
-                <a:moveTo>
-                  <a:pt x="91706" y="6096000"/>
-                </a:moveTo>
-                <a:cubicBezTo>
-                  <a:pt x="10743" y="4841875"/>
-                  <a:pt x="-70219" y="3587750"/>
-                  <a:pt x="101231" y="2571750"/>
-                </a:cubicBezTo>
-                <a:cubicBezTo>
-                  <a:pt x="272681" y="1555750"/>
-                  <a:pt x="993406" y="392112"/>
-                  <a:pt x="1120406" y="0"/>
-                </a:cubicBezTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="27" name="楕円 26">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FF919B0-587B-F9FB-A742-3FE13DF713DD}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="10068826" y="2308412"/>
-            <a:ext cx="1812439" cy="1694328"/>
-          </a:xfrm>
-          <a:prstGeom prst="ellipse">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="27843"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="28" name="楕円 27">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76DD2FBB-8482-56CB-870A-F70A0FFF6A8C}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5636339" y="2630581"/>
-            <a:ext cx="1814680" cy="1691528"/>
-          </a:xfrm>
-          <a:prstGeom prst="ellipse">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="27843"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="29" name="楕円 28">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{130EA62D-6B01-D461-384F-DE9985BF7E16}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="10931118" y="3141569"/>
-            <a:ext cx="1810198" cy="1694329"/>
-          </a:xfrm>
-          <a:prstGeom prst="ellipse">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="27843"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="30" name="楕円 29">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EE87350-BB64-D621-5DEF-40840530CDA8}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="6893639" y="3257550"/>
-            <a:ext cx="1812439" cy="1688726"/>
-          </a:xfrm>
-          <a:prstGeom prst="ellipse">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="27843"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="31" name="フリーフォーム: 図形 30">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E425276B-DE84-CC4D-28D3-943DE72D7601}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="20023133" flipH="1">
-            <a:off x="10218076" y="1461394"/>
-            <a:ext cx="489665" cy="1863170"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-              <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-              <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-              <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-              <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-              <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX0" y="connsiteY0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX1" y="connsiteY1"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX2" y="connsiteY2"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="l" t="t" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="1120406" h="6096000">
-                <a:moveTo>
-                  <a:pt x="91706" y="6096000"/>
-                </a:moveTo>
-                <a:cubicBezTo>
-                  <a:pt x="10743" y="4841875"/>
-                  <a:pt x="-70219" y="3587750"/>
-                  <a:pt x="101231" y="2571750"/>
-                </a:cubicBezTo>
-                <a:cubicBezTo>
-                  <a:pt x="272681" y="1555750"/>
-                  <a:pt x="993406" y="392112"/>
-                  <a:pt x="1120406" y="0"/>
-                </a:cubicBezTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="32" name="フリーフォーム: 図形 31">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34D5AC5D-99B9-F973-6CAB-2949D4D54AF4}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="1226854">
-            <a:off x="8231636" y="1459818"/>
-            <a:ext cx="902441" cy="2815356"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-              <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-              <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-              <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-              <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-              <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX0" y="connsiteY0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX1" y="connsiteY1"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX2" y="connsiteY2"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="l" t="t" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="1120406" h="6096000">
-                <a:moveTo>
-                  <a:pt x="91706" y="6096000"/>
-                </a:moveTo>
-                <a:cubicBezTo>
-                  <a:pt x="10743" y="4841875"/>
-                  <a:pt x="-70219" y="3587750"/>
-                  <a:pt x="101231" y="2571750"/>
-                </a:cubicBezTo>
-                <a:cubicBezTo>
-                  <a:pt x="272681" y="1555750"/>
-                  <a:pt x="993406" y="392112"/>
-                  <a:pt x="1120406" y="0"/>
-                </a:cubicBezTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>100633</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>78441</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>593912</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>228599</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="33" name="グループ化 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{539AD1DA-04CD-B747-401A-9291A4CBF1AC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="5569104" y="4078941"/>
-          <a:ext cx="3911073" cy="2268070"/>
-          <a:chOff x="5636339" y="1459818"/>
-          <a:chExt cx="7104977" cy="3486458"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="34" name="フリーフォーム: 図形 33">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFEC5F89-34D7-757A-93E8-3786EA8288B1}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="2833576">
-            <a:off x="7648320" y="836209"/>
-            <a:ext cx="536972" cy="3303762"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-              <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-              <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-              <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-              <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-              <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX0" y="connsiteY0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX1" y="connsiteY1"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX2" y="connsiteY2"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="l" t="t" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="1120406" h="6096000">
-                <a:moveTo>
-                  <a:pt x="91706" y="6096000"/>
-                </a:moveTo>
-                <a:cubicBezTo>
-                  <a:pt x="10743" y="4841875"/>
-                  <a:pt x="-70219" y="3587750"/>
-                  <a:pt x="101231" y="2571750"/>
-                </a:cubicBezTo>
-                <a:cubicBezTo>
-                  <a:pt x="272681" y="1555750"/>
-                  <a:pt x="993406" y="392112"/>
-                  <a:pt x="1120406" y="0"/>
-                </a:cubicBezTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="35" name="フリーフォーム: 図形 34">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{331ED467-D631-8741-8ACF-9FC0C78D6C05}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="7202030">
-            <a:off x="10284991" y="1165680"/>
-            <a:ext cx="1306134" cy="3029338"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-              <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-              <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-              <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-              <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-              <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX0" y="connsiteY0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX1" y="connsiteY1"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX2" y="connsiteY2"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="l" t="t" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="1120406" h="6096000">
-                <a:moveTo>
-                  <a:pt x="91706" y="6096000"/>
-                </a:moveTo>
-                <a:cubicBezTo>
-                  <a:pt x="10743" y="4841875"/>
-                  <a:pt x="-70219" y="3587750"/>
-                  <a:pt x="101231" y="2571750"/>
-                </a:cubicBezTo>
-                <a:cubicBezTo>
-                  <a:pt x="272681" y="1555750"/>
-                  <a:pt x="993406" y="392112"/>
-                  <a:pt x="1120406" y="0"/>
-                </a:cubicBezTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="36" name="楕円 35">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0775993-9B6F-C299-C61A-CD2A545453A2}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="10068826" y="2308412"/>
-            <a:ext cx="1812439" cy="1694328"/>
-          </a:xfrm>
-          <a:prstGeom prst="ellipse">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="27843"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="37" name="楕円 36">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CADECB46-C6B8-3E74-F12C-DB2F3D9F8468}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5636339" y="2630581"/>
-            <a:ext cx="1814680" cy="1691528"/>
-          </a:xfrm>
-          <a:prstGeom prst="ellipse">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="27843"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="38" name="楕円 37">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EB4E7CC-C2D6-4F29-4CED-981C6CD8266B}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="10931118" y="3141569"/>
-            <a:ext cx="1810198" cy="1694329"/>
-          </a:xfrm>
-          <a:prstGeom prst="ellipse">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="27843"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="39" name="楕円 38">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D22E5FB-D0C8-DB0A-420E-55BDED467A6E}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="6893639" y="3257550"/>
-            <a:ext cx="1812439" cy="1688726"/>
-          </a:xfrm>
-          <a:prstGeom prst="ellipse">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="27843"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="40" name="フリーフォーム: 図形 39">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1384222A-43BA-89CB-5FE1-FE6436A20F6C}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="20023133" flipH="1">
-            <a:off x="10218076" y="1461394"/>
-            <a:ext cx="489665" cy="1863170"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-              <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-              <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-              <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-              <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-              <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX0" y="connsiteY0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX1" y="connsiteY1"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX2" y="connsiteY2"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="l" t="t" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="1120406" h="6096000">
-                <a:moveTo>
-                  <a:pt x="91706" y="6096000"/>
-                </a:moveTo>
-                <a:cubicBezTo>
-                  <a:pt x="10743" y="4841875"/>
-                  <a:pt x="-70219" y="3587750"/>
-                  <a:pt x="101231" y="2571750"/>
-                </a:cubicBezTo>
-                <a:cubicBezTo>
-                  <a:pt x="272681" y="1555750"/>
-                  <a:pt x="993406" y="392112"/>
-                  <a:pt x="1120406" y="0"/>
-                </a:cubicBezTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="41" name="フリーフォーム: 図形 40">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BB128E1-59DC-093E-6A5B-C599D53E049A}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="1226854">
-            <a:off x="8231636" y="1459818"/>
-            <a:ext cx="902441" cy="2815356"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-              <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-              <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-              <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-              <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-              <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX0" y="connsiteY0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX1" y="connsiteY1"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX2" y="connsiteY2"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="l" t="t" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="1120406" h="6096000">
-                <a:moveTo>
-                  <a:pt x="91706" y="6096000"/>
-                </a:moveTo>
-                <a:cubicBezTo>
-                  <a:pt x="10743" y="4841875"/>
-                  <a:pt x="-70219" y="3587750"/>
-                  <a:pt x="101231" y="2571750"/>
-                </a:cubicBezTo>
-                <a:cubicBezTo>
-                  <a:pt x="272681" y="1555750"/>
-                  <a:pt x="993406" y="392112"/>
-                  <a:pt x="1120406" y="0"/>
-                </a:cubicBezTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>235104</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>78442</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>44824</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="42" name="グループ化 41">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F37E445-4FC2-7E99-D3E8-34928A5A02B2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="4336457" y="3372971"/>
-          <a:ext cx="3911073" cy="2268070"/>
-          <a:chOff x="5636339" y="1459818"/>
-          <a:chExt cx="7104977" cy="3486458"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="43" name="フリーフォーム: 図形 42">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48432E28-B2CE-8F2A-F217-58EE9A5AB9F2}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="2833576">
-            <a:off x="7648320" y="836209"/>
-            <a:ext cx="536972" cy="3303762"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-              <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-              <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-              <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-              <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-              <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX0" y="connsiteY0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX1" y="connsiteY1"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX2" y="connsiteY2"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="l" t="t" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="1120406" h="6096000">
-                <a:moveTo>
-                  <a:pt x="91706" y="6096000"/>
-                </a:moveTo>
-                <a:cubicBezTo>
-                  <a:pt x="10743" y="4841875"/>
-                  <a:pt x="-70219" y="3587750"/>
-                  <a:pt x="101231" y="2571750"/>
-                </a:cubicBezTo>
-                <a:cubicBezTo>
-                  <a:pt x="272681" y="1555750"/>
-                  <a:pt x="993406" y="392112"/>
-                  <a:pt x="1120406" y="0"/>
-                </a:cubicBezTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="44" name="フリーフォーム: 図形 43">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA223C9F-5CD6-08E4-899C-94B9CF310EB7}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="7202030">
-            <a:off x="10284991" y="1165680"/>
-            <a:ext cx="1306134" cy="3029338"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-              <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-              <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-              <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-              <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-              <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX0" y="connsiteY0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX1" y="connsiteY1"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX2" y="connsiteY2"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="l" t="t" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="1120406" h="6096000">
-                <a:moveTo>
-                  <a:pt x="91706" y="6096000"/>
-                </a:moveTo>
-                <a:cubicBezTo>
-                  <a:pt x="10743" y="4841875"/>
-                  <a:pt x="-70219" y="3587750"/>
-                  <a:pt x="101231" y="2571750"/>
-                </a:cubicBezTo>
-                <a:cubicBezTo>
-                  <a:pt x="272681" y="1555750"/>
-                  <a:pt x="993406" y="392112"/>
-                  <a:pt x="1120406" y="0"/>
-                </a:cubicBezTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="45" name="楕円 44">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3689131-79D5-982F-3723-C3E952357027}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="10068826" y="2308412"/>
-            <a:ext cx="1812439" cy="1694328"/>
-          </a:xfrm>
-          <a:prstGeom prst="ellipse">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="27843"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="46" name="楕円 45">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DED00BF2-BDF9-13B5-2B8B-3CACD0B2AFE2}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5636339" y="2630581"/>
-            <a:ext cx="1814680" cy="1691528"/>
-          </a:xfrm>
-          <a:prstGeom prst="ellipse">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="27843"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="47" name="楕円 46">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDBE7ECD-FAD4-2AE8-34BA-7A9E74492984}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="10931118" y="3141569"/>
-            <a:ext cx="1810198" cy="1694329"/>
-          </a:xfrm>
-          <a:prstGeom prst="ellipse">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="27843"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="48" name="楕円 47">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FBDF33C0-CAEB-E7AB-B5A3-AB6D4A2B9151}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="6893639" y="3257550"/>
-            <a:ext cx="1812439" cy="1688726"/>
-          </a:xfrm>
-          <a:prstGeom prst="ellipse">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="4472C4">
-              <a:alpha val="27843"/>
-            </a:srgbClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="49" name="フリーフォーム: 図形 48">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BECFCAD1-D9F0-3B27-656B-9F9CEE7DF022}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="20023133" flipH="1">
-            <a:off x="10218076" y="1461394"/>
-            <a:ext cx="489665" cy="1863170"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-              <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-              <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-              <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-              <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-              <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX0" y="connsiteY0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX1" y="connsiteY1"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX2" y="connsiteY2"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="l" t="t" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="1120406" h="6096000">
-                <a:moveTo>
-                  <a:pt x="91706" y="6096000"/>
-                </a:moveTo>
-                <a:cubicBezTo>
-                  <a:pt x="10743" y="4841875"/>
-                  <a:pt x="-70219" y="3587750"/>
-                  <a:pt x="101231" y="2571750"/>
-                </a:cubicBezTo>
-                <a:cubicBezTo>
-                  <a:pt x="272681" y="1555750"/>
-                  <a:pt x="993406" y="392112"/>
-                  <a:pt x="1120406" y="0"/>
-                </a:cubicBezTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="50" name="フリーフォーム: 図形 49">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{060DDBFF-C9E9-B4E2-F21E-90D51151AB86}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="1226854">
-            <a:off x="8231636" y="1459818"/>
-            <a:ext cx="902441" cy="2815356"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="connsiteX0" fmla="*/ 91706 w 1120406"/>
-              <a:gd name="connsiteY0" fmla="*/ 6096000 h 6096000"/>
-              <a:gd name="connsiteX1" fmla="*/ 101231 w 1120406"/>
-              <a:gd name="connsiteY1" fmla="*/ 2571750 h 6096000"/>
-              <a:gd name="connsiteX2" fmla="*/ 1120406 w 1120406"/>
-              <a:gd name="connsiteY2" fmla="*/ 0 h 6096000"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX0" y="connsiteY0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX1" y="connsiteY1"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="connsiteX2" y="connsiteY2"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="l" t="t" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="1120406" h="6096000">
-                <a:moveTo>
-                  <a:pt x="91706" y="6096000"/>
-                </a:moveTo>
-                <a:cubicBezTo>
-                  <a:pt x="10743" y="4841875"/>
-                  <a:pt x="-70219" y="3587750"/>
-                  <a:pt x="101231" y="2571750"/>
-                </a:cubicBezTo>
-                <a:cubicBezTo>
-                  <a:pt x="272681" y="1555750"/>
-                  <a:pt x="993406" y="392112"/>
-                  <a:pt x="1120406" y="0"/>
-                </a:cubicBezTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -14187,213 +7660,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F5E3C13-9D9E-4DB6-8310-05DD94B1E700}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2867894-1ECB-440B-B7F1-C920D874DA99}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E978B7C6-D216-4C1C-95C2-35B6DB7EAB2C}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACC24685-9DCE-4541-B24E-9FADAF4B003D}">
-  <dimension ref="A1:A20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>115</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{080C3E38-ADE2-4C9D-A7A5-419688E8A3B4}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D6350D8-1E92-453A-AC2E-9E0AE9B59452}">
-  <dimension ref="K2:K11"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData>
-    <row r="2" spans="11:11" x14ac:dyDescent="0.4">
-      <c r="K2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="3" spans="11:11" x14ac:dyDescent="0.4">
-      <c r="K3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="4" spans="11:11" x14ac:dyDescent="0.4">
-      <c r="K4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" spans="11:11" x14ac:dyDescent="0.4">
-      <c r="K5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="7" spans="11:11" x14ac:dyDescent="0.4">
-      <c r="K7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="8" spans="11:11" x14ac:dyDescent="0.4">
-      <c r="K8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="11:11" x14ac:dyDescent="0.4">
-      <c r="K9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="11:11" x14ac:dyDescent="0.4">
-      <c r="K10" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="11" spans="11:11" x14ac:dyDescent="0.4">
-      <c r="K11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B64922A4-6BE5-4467-824C-7472AFCA4E83}">
   <dimension ref="B1:C38"/>
@@ -14732,7 +7998,7 @@
         <v>45</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F12" t="s">
         <v>89</v>
@@ -14885,67 +8151,67 @@
   <sheetData>
     <row r="5" spans="6:13" x14ac:dyDescent="0.4">
       <c r="K5" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="6:13" x14ac:dyDescent="0.4">
       <c r="K6" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="6:13" x14ac:dyDescent="0.4">
       <c r="M8" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="6:13" x14ac:dyDescent="0.4">
       <c r="M10" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="6:13" x14ac:dyDescent="0.4">
       <c r="M11" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="6:13" x14ac:dyDescent="0.4">
       <c r="M12" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="6:13" x14ac:dyDescent="0.4">
       <c r="F13" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="6:13" x14ac:dyDescent="0.4">
       <c r="M16" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="6:13" x14ac:dyDescent="0.4">
       <c r="M17" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="6:13" x14ac:dyDescent="0.4">
       <c r="M18" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="6:13" x14ac:dyDescent="0.4">
       <c r="M19" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="6:13" x14ac:dyDescent="0.4">
       <c r="M21" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="6:13" x14ac:dyDescent="0.4">
       <c r="F24" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -14956,18 +8222,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79A98CD3-681F-455F-98DC-5CB2DD3850CC}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD321CFD-8D11-4936-BD98-B370B88A1A26}">
   <dimension ref="L4:P24"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -15052,21 +8306,4 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD7A96E6-131F-4879-A224-7B85E82A899C}">
-  <dimension ref="C1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData>
-    <row r="1" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>